--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="C2" t="n">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.028017</v>
+        <v>0.019404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.180364</v>
+        <v>0.158605</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07244399999999999</v>
+        <v>0.061875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.766024</v>
+        <v>0.626995</v>
       </c>
       <c r="H2" t="n">
-        <v>0.865683</v>
+        <v>0.770159</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="C3" t="n">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.023954</v>
+        <v>0.013458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.120935</v>
+        <v>0.09499</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06408800000000001</v>
+        <v>0.05526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.38559</v>
+        <v>0.298671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.601285</v>
+        <v>0.35213</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.004063</v>
+        <v>-0.005946</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.059429</v>
+        <v>-0.063615</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.008356000000000001</v>
+        <v>-0.006615</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.380434</v>
+        <v>-0.328324</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.264398</v>
+        <v>-0.418029</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="C2" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="D2" t="n">
-        <v>0.019404</v>
+        <v>0.02126</v>
       </c>
       <c r="E2" t="n">
-        <v>0.158605</v>
+        <v>0.162249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061875</v>
+        <v>0.063027</v>
       </c>
       <c r="G2" t="n">
-        <v>0.626995</v>
+        <v>0.63491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.770159</v>
+        <v>0.774709</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>752</v>
+        <v>695</v>
       </c>
       <c r="C3" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013458</v>
+        <v>0.014867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09499</v>
+        <v>0.09605900000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05526</v>
+        <v>0.057513</v>
       </c>
       <c r="G3" t="n">
-        <v>0.298671</v>
+        <v>0.280086</v>
       </c>
       <c r="H3" t="n">
-        <v>0.35213</v>
+        <v>0.357118</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.005946</v>
+        <v>-0.006393</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.063615</v>
+        <v>-0.06619</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006615</v>
+        <v>-0.005514</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.328324</v>
+        <v>-0.354824</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.418029</v>
+        <v>-0.417591</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="C2" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02126</v>
+        <v>0.023535</v>
       </c>
       <c r="E2" t="n">
-        <v>0.162249</v>
+        <v>0.165835</v>
       </c>
       <c r="F2" t="n">
-        <v>0.063027</v>
+        <v>0.066471</v>
       </c>
       <c r="G2" t="n">
-        <v>0.63491</v>
+        <v>0.654959</v>
       </c>
       <c r="H2" t="n">
-        <v>0.774709</v>
+        <v>0.744555</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="C3" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014867</v>
+        <v>0.016553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09605900000000001</v>
+        <v>0.09955600000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.057513</v>
+        <v>0.057505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.280086</v>
+        <v>0.339415</v>
       </c>
       <c r="H3" t="n">
-        <v>0.357118</v>
+        <v>0.388032</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.006393</v>
+        <v>-0.006982</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06619</v>
+        <v>-0.066279</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005514</v>
+        <v>-0.008966</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.354824</v>
+        <v>-0.315544</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.417591</v>
+        <v>-0.356523</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023535</v>
+        <v>0.023657</v>
       </c>
       <c r="E2" t="n">
-        <v>0.165835</v>
+        <v>0.166206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.066471</v>
+        <v>0.06464300000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.654959</v>
+        <v>0.67306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.744555</v>
+        <v>0.742665</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C3" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D3" t="n">
-        <v>0.016553</v>
+        <v>0.016371</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09955600000000001</v>
+        <v>0.09810199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.057505</v>
+        <v>0.0559</v>
       </c>
       <c r="G3" t="n">
-        <v>0.339415</v>
+        <v>0.335623</v>
       </c>
       <c r="H3" t="n">
-        <v>0.388032</v>
+        <v>0.384908</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.006982</v>
+        <v>-0.007286</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.066279</v>
+        <v>-0.068104</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.008966</v>
+        <v>-0.008743000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.315544</v>
+        <v>-0.337437</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.356523</v>
+        <v>-0.357757</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C2" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023657</v>
+        <v>0.027268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.166206</v>
+        <v>0.165768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06464300000000001</v>
+        <v>0.061748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.67306</v>
+        <v>0.673009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.742665</v>
+        <v>0.741044</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C3" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.016371</v>
+        <v>0.014851</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09810199999999999</v>
+        <v>0.07604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0559</v>
+        <v>0.051469</v>
       </c>
       <c r="G3" t="n">
-        <v>0.335623</v>
+        <v>0.25364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.384908</v>
+        <v>0.314223</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.007286</v>
+        <v>-0.012417</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.068104</v>
+        <v>-0.089728</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.008743000000000001</v>
+        <v>-0.010279</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.337437</v>
+        <v>-0.419369</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.357757</v>
+        <v>-0.426821</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C2" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027268</v>
+        <v>0.024576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.165768</v>
+        <v>0.135997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061748</v>
+        <v>0.061784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.673009</v>
+        <v>0.672434</v>
       </c>
       <c r="H2" t="n">
-        <v>0.741044</v>
+        <v>0.711338</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014851</v>
+        <v>0.014633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07604</v>
+        <v>0.07030699999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.051469</v>
+        <v>0.04982</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25364</v>
+        <v>0.230509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.314223</v>
+        <v>0.277584</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.012417</v>
+        <v>-0.009943</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.089728</v>
+        <v>-0.06569</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.010279</v>
+        <v>-0.011964</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.419369</v>
+        <v>-0.441925</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.426821</v>
+        <v>-0.433754</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C2" t="n">
         <v>376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.024576</v>
+        <v>0.02454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.135997</v>
+        <v>0.135901</v>
       </c>
       <c r="F2" t="n">
         <v>0.061784</v>
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C3" t="n">
         <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014633</v>
+        <v>0.014611</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07030699999999999</v>
+        <v>0.070258</v>
       </c>
       <c r="F3" t="n">
         <v>0.04982</v>
@@ -523,10 +523,10 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.009943</v>
+        <v>-0.009929</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06569</v>
+        <v>-0.06564300000000001</v>
       </c>
       <c r="F4" t="n">
         <v>-0.011964</v>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014611</v>
+        <v>0.014714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.070258</v>
+        <v>0.070872</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04982</v>
+        <v>0.050274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.230509</v>
+        <v>0.232207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.277584</v>
+        <v>0.279905</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.009929</v>
+        <v>-0.009826</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06564300000000001</v>
+        <v>-0.065029</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.011964</v>
+        <v>-0.01151</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.441925</v>
+        <v>-0.440227</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.433754</v>
+        <v>-0.431433</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="C2" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02454</v>
+        <v>0.023161</v>
       </c>
       <c r="E2" t="n">
-        <v>0.135901</v>
+        <v>0.136611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061784</v>
+        <v>0.061712</v>
       </c>
       <c r="G2" t="n">
         <v>0.672434</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="C3" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.014714</v>
+        <v>0.015555</v>
       </c>
       <c r="E3" t="n">
-        <v>0.070872</v>
+        <v>0.079725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.050274</v>
+        <v>0.055705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.232207</v>
+        <v>0.265808</v>
       </c>
       <c r="H3" t="n">
-        <v>0.279905</v>
+        <v>0.30141</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.009826</v>
+        <v>-0.007606</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.065029</v>
+        <v>-0.056886</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01151</v>
+        <v>-0.006007</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.440227</v>
+        <v>-0.406626</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.431433</v>
+        <v>-0.409928</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,22 +465,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="C2" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023161</v>
+        <v>0.023407</v>
       </c>
       <c r="E2" t="n">
-        <v>0.136611</v>
+        <v>0.130427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061712</v>
+        <v>0.060827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.672434</v>
+        <v>0.634074</v>
       </c>
       <c r="H2" t="n">
         <v>0.711338</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015555</v>
+        <v>0.015553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.079725</v>
+        <v>0.079917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.055705</v>
+        <v>0.055481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.265808</v>
+        <v>0.264434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.30141</v>
+        <v>0.298916</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.007606</v>
+        <v>-0.007854</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.056886</v>
+        <v>-0.05051</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006007</v>
+        <v>-0.005346</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.406626</v>
+        <v>-0.36964</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.409928</v>
+        <v>-0.412422</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -468,19 +468,19 @@
         <v>674</v>
       </c>
       <c r="C2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023407</v>
+        <v>0.02272</v>
       </c>
       <c r="E2" t="n">
-        <v>0.130427</v>
+        <v>0.125546</v>
       </c>
       <c r="F2" t="n">
         <v>0.060827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.634074</v>
+        <v>0.620194</v>
       </c>
       <c r="H2" t="n">
         <v>0.711338</v>
@@ -496,22 +496,22 @@
         <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015553</v>
+        <v>0.015467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.079917</v>
+        <v>0.07892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.055481</v>
+        <v>0.055231</v>
       </c>
       <c r="G3" t="n">
-        <v>0.264434</v>
+        <v>0.260987</v>
       </c>
       <c r="H3" t="n">
-        <v>0.298916</v>
+        <v>0.295407</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.007854</v>
+        <v>-0.007253</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05051</v>
+        <v>-0.046626</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005346</v>
+        <v>-0.005596</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.36964</v>
+        <v>-0.359207</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.412422</v>
+        <v>-0.415931</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015467</v>
+        <v>0.015494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07892</v>
+        <v>0.078954</v>
       </c>
       <c r="F3" t="n">
-        <v>0.055231</v>
+        <v>0.055216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.260987</v>
+        <v>0.257932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.295407</v>
+        <v>0.295159</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.007253</v>
+        <v>-0.007226</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.046626</v>
+        <v>-0.046592</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005596</v>
+        <v>-0.005611</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.359207</v>
+        <v>-0.362262</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.415931</v>
+        <v>-0.416179</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C2" t="n">
         <v>368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02272</v>
+        <v>0.022803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.125546</v>
+        <v>0.125749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C3" t="n">
         <v>368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015494</v>
+        <v>0.015612</v>
       </c>
       <c r="E3" t="n">
-        <v>0.078954</v>
+        <v>0.079195</v>
       </c>
       <c r="F3" t="n">
-        <v>0.055216</v>
+        <v>0.055168</v>
       </c>
       <c r="G3" t="n">
-        <v>0.257932</v>
+        <v>0.256726</v>
       </c>
       <c r="H3" t="n">
-        <v>0.295159</v>
+        <v>0.295054</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.007226</v>
+        <v>-0.007191</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.046592</v>
+        <v>-0.046554</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005611</v>
+        <v>-0.005714</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.362262</v>
+        <v>-0.363468</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.416179</v>
+        <v>-0.416284</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="C2" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D2" t="n">
-        <v>0.022803</v>
+        <v>0.02764</v>
       </c>
       <c r="E2" t="n">
-        <v>0.125749</v>
+        <v>0.117607</v>
       </c>
       <c r="F2" t="n">
-        <v>0.060882</v>
+        <v>0.059367</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="C3" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D3" t="n">
-        <v>0.015612</v>
+        <v>0.02122</v>
       </c>
       <c r="E3" t="n">
-        <v>0.079195</v>
+        <v>0.07353700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.055168</v>
+        <v>0.054584</v>
       </c>
       <c r="G3" t="n">
-        <v>0.256726</v>
+        <v>0.263619</v>
       </c>
       <c r="H3" t="n">
-        <v>0.295054</v>
+        <v>0.330368</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.007191</v>
+        <v>-0.00642</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.046554</v>
+        <v>-0.04407</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005714</v>
+        <v>-0.004783</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.363468</v>
+        <v>-0.356575</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.416284</v>
+        <v>-0.38097</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -499,19 +499,19 @@
         <v>398</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02122</v>
+        <v>0.02123</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07353700000000001</v>
+        <v>0.07356500000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.054584</v>
+        <v>0.054603</v>
       </c>
       <c r="G3" t="n">
-        <v>0.263619</v>
+        <v>0.263815</v>
       </c>
       <c r="H3" t="n">
-        <v>0.330368</v>
+        <v>0.33048</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.00642</v>
+        <v>-0.00641</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04407</v>
+        <v>-0.044042</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.004783</v>
+        <v>-0.004764</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.356575</v>
+        <v>-0.356379</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.38097</v>
+        <v>-0.380858</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,19 +465,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C2" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02764</v>
+        <v>0.027314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.117607</v>
+        <v>0.11606</v>
       </c>
       <c r="F2" t="n">
-        <v>0.059367</v>
+        <v>0.058745</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C3" t="n">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02123</v>
+        <v>0.020834</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07356500000000001</v>
+        <v>0.072801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.054603</v>
+        <v>0.054064</v>
       </c>
       <c r="G3" t="n">
-        <v>0.263815</v>
+        <v>0.266966</v>
       </c>
       <c r="H3" t="n">
-        <v>0.33048</v>
+        <v>0.334027</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.00641</v>
+        <v>-0.00648</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.044042</v>
+        <v>-0.043259</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.004764</v>
+        <v>-0.004681</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.356379</v>
+        <v>-0.353228</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.380858</v>
+        <v>-0.377311</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -471,13 +471,13 @@
         <v>394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027314</v>
+        <v>0.027338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11606</v>
+        <v>0.116067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
       <c r="G2" t="n">
         <v>0.620194</v>
@@ -499,19 +499,19 @@
         <v>394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.020834</v>
+        <v>0.020864</v>
       </c>
       <c r="E3" t="n">
-        <v>0.072801</v>
+        <v>0.072835</v>
       </c>
       <c r="F3" t="n">
-        <v>0.054064</v>
+        <v>0.054413</v>
       </c>
       <c r="G3" t="n">
-        <v>0.266966</v>
+        <v>0.267257</v>
       </c>
       <c r="H3" t="n">
-        <v>0.334027</v>
+        <v>0.334312</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.00648</v>
+        <v>-0.006474</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.043259</v>
+        <v>-0.043232</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.004681</v>
+        <v>-0.004423</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.353228</v>
+        <v>-0.352937</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.377311</v>
+        <v>-0.377026</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/distribution_stats.xlsx
+++ b/vignettes/vignette-1/distribution_stats.xlsx
@@ -465,25 +465,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="C2" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D2" t="n">
-        <v>0.027338</v>
+        <v>0.026645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.116067</v>
+        <v>0.112082</v>
       </c>
       <c r="F2" t="n">
-        <v>0.058836</v>
+        <v>0.058745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.620194</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
     </row>
     <row r="3">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="C3" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" t="n">
-        <v>0.020864</v>
+        <v>0.021057</v>
       </c>
       <c r="E3" t="n">
-        <v>0.072835</v>
+        <v>0.07341499999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.054413</v>
+        <v>0.054108</v>
       </c>
       <c r="G3" t="n">
-        <v>0.267257</v>
+        <v>0.276042</v>
       </c>
       <c r="H3" t="n">
-        <v>0.334312</v>
+        <v>0.3424</v>
       </c>
     </row>
     <row r="4">
@@ -523,19 +523,19 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-0.006474</v>
+        <v>-0.005588</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.043232</v>
+        <v>-0.038667</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.004423</v>
+        <v>-0.004637</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.352937</v>
+        <v>-0.328895</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.377026</v>
+        <v>-0.330034</v>
       </c>
     </row>
   </sheetData>
